--- a/main/ig/StructureDefinition-CapaciteSavoirfaire.xlsx
+++ b/main/ig/StructureDefinition-CapaciteSavoirfaire.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:56:39+00:00</t>
+    <t>2026-06-26T11:59:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-CapaciteSavoirfaire.xlsx
+++ b/main/ig/StructureDefinition-CapaciteSavoirfaire.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:59:32+00:00</t>
+    <t>2026-10-15T15:04:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
